--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -1005,6 +1005,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215927806293937</t>
@@ -7288,7 +7291,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.58682732639</v>
+        <v>46280.136757025466</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>298</v>
@@ -7332,8 +7335,8 @@
       <c r="R101" s="8">
         <v>46287</v>
       </c>
-      <c r="S101" s="11" t="s">
-        <v>108</v>
+      <c r="S101" s="12" t="s">
+        <v>301</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
@@ -7344,17 +7347,17 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.58676837963</v>
+        <v>46280.13675539352</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7395,8 +7398,8 @@
       <c r="R102" s="5">
         <v>46287</v>
       </c>
-      <c r="S102" s="11" t="s">
-        <v>108</v>
+      <c r="S102" s="12" t="s">
+        <v>301</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
